--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:12:38+00:00</t>
+    <t>2026-09-14T19:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:45:33+00:00</t>
+    <t>2026-09-14T20:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:15:28+00:00</t>
+    <t>2026-09-14T20:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:43:02+00:00</t>
+    <t>2026-09-14T21:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:08:50+00:00</t>
+    <t>2026-09-14T21:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:38:27+00:00</t>
+    <t>2026-09-14T22:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
+++ b/branches/chore/onko-ballot-repin/ValueSet-mii-vs-mtb-ish-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:18:02+00:00</t>
+    <t>2026-09-14T22:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
